--- a/missionary_forms/003_international_missions_form--missionary_forms.xlsx
+++ b/missionary_forms/003_international_missions_form--missionary_forms.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -430,10 +440,10 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>international_missions_form_page_1</t>
+          <t>mission_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>International Missions Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Mission Details</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of the mission's objectives, goals, and scope.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -528,43 +542,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>international_missions_form_page_2</t>
+          <t>mission_dates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Missionary Form Data</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Mission Dates</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Specify the start and end dates of the mission.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>international_missions_form_page_3</t>
+          <t>mission_locations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mission Details</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Mission Locations</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>List the countries or regions where the mission will take place.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -579,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>international_missions_form_page_4</t>
+          <t>mission_expenses</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mission Dates</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Mission Expenses</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estimate the total expenses for the mission, including travel, accommodation, and other costs.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,38 +628,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>international_missions_form_page_5</t>
+          <t>expenses_per_day</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mission Times</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Expenses Per Day</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Break down the estimated expenses per day of the mission.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>international_missions_form_page_6</t>
+          <t>mission_expenses_category</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mission Locations</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Mission Expenses Category</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Identify the category or categories of expenses, such as food, transportation, and equipment.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -648,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>international_missions_form_page_7</t>
+          <t>mission_objectives</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mission Expenses</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Mission Objectives</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Describe the mission's primary objectives, outcomes, or deliverables.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>international_missions_form_page_8</t>
+          <t>mission_duration</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mission Expenses Total</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Mission Duration</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Specify the duration of the mission, including the number of days or weeks.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>international_missions_form_page_9</t>
+          <t>mission_team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Expenses Per Day</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Mission Team</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>List the team members involved in the mission, including their roles and responsibilities.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -717,38 +763,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>international_missions_form_page_10</t>
+          <t>mission_risks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mission Expenses Category</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Mission Risks</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Identify potential risks or challenges associated with the mission.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>international_missions_form_page_11</t>
+          <t>mission_success_criteria</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mission Dates</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Mission Success Criteria</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Define the criteria for measuring the mission's success.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -763,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>international_missions_form_page_12</t>
+          <t>mission_evaluation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mission Dates</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Mission Evaluation</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Evaluate the mission's progress and outcomes.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -786,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>international_missions_form_page_13</t>
+          <t>mission_dates_confirmation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mission Times</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Confirm Mission Dates</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Confirm the mission dates provided.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -809,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>international_missions_form_page_14</t>
+          <t>mission_locations_confirmation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mission Expenses Category</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Confirm Mission Locations</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Confirm the mission locations provided.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -832,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>international_missions_form_page_15</t>
+          <t>mission_expenses_confirmation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mission Dates</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Confirm Mission Expenses</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Confirm the mission expenses provided.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -855,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>international_missions_form_page_16</t>
+          <t>mission_expenses_category_confirmation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mission Locations</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Confirm Mission Expenses Category</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Confirm the mission expenses category provided.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -873,20 +947,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>international_missions_form_page_17</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mission Times</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Provide any additional information or comments.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -901,18 +979,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>international_missions_form_page_18</t>
+          <t>confirmation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mission Expenses Total</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Confirmation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please confirm that the form is complete and accurate.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -922,6 +1004,314 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mission_locations_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mission_locations_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mission_locations_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mission_locations_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mission_locations_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>option_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Option 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mission_locations_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>option_6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Option 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mission_locations_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>option_7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Option 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mission_expenses_category_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mission_expenses_category_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mission_expenses_category_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mission_expenses_category_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mission_expenses_category_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>option_5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Option 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mission_success_criteria_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mission_success_criteria_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mission_success_criteria_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mission_success_criteria_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
